--- a/output/full_scan/batch_seq8_2026-07-15.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-15.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8024</v>
+        <v>8021</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>760.8620290172038</v>
+        <v>766.0372016869778</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.2</v>
+        <v>532</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.57828121016621</v>
+        <v>52.86053780648466</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>40.46232896979892</v>
+        <v>16.064939177237</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6189237924840704</v>
+        <v>0.3928944059338367</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0968278624581924</v>
+        <v>-8.507273842984652</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6957</v>
+        <v>8024</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>726.3228304833992</v>
+        <v>760.8620290172038</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>238</v>
+        <v>17.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>81.47432646419801</v>
+        <v>68.57828121016621</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>37.34377643532943</v>
+        <v>40.46232896979892</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.279704220207893</v>
+        <v>0.6189237924840704</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.5149448225791</v>
+        <v>0.0968278624581924</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7610</v>
+        <v>6957</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>684.2621387884541</v>
+        <v>726.3228304833992</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2430</v>
+        <v>238</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.11172740894829</v>
+        <v>81.47432646419801</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>36.58410659635899</v>
+        <v>37.34377643532943</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.9846424538081094</v>
+        <v>2.279704220207893</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-34.17080113879439</v>
+        <v>3.5149448225791</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6901</v>
+        <v>8033</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>671.832742270949</v>
+        <v>722.2936533404211</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.25</v>
+        <v>269.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.49488010555067</v>
+        <v>85.29796387773349</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>48.98571642589341</v>
+        <v>41.72123919021907</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5233193207998004</v>
+        <v>0.4681694322597041</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.059625605524296</v>
+        <v>10.0776606481181</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6958</v>
+        <v>7610</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>643.7701196027724</v>
+        <v>684.2621387884541</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>18.5</v>
+        <v>2430</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>67.08381189388399</v>
+        <v>60.11172740894829</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.46667127807536</v>
+        <v>36.58410659635899</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.843235954600524</v>
+        <v>0.9846424538081094</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1516390527204662</v>
+        <v>-34.17080113879439</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8016</v>
+        <v>6901</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>623.8958654419929</v>
+        <v>671.832742270949</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>302</v>
+        <v>19.25</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45.00580870824002</v>
+        <v>59.49488010555067</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.69694170850491</v>
+        <v>48.98571642589341</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.4997884454218033</v>
+        <v>0.5233193207998004</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-3.965880053293586</v>
+        <v>-0.059625605524296</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6907</v>
+        <v>6958</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>616.2046470660028</v>
+        <v>643.7701196027724</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>232.5</v>
+        <v>18.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>75.60165797176452</v>
+        <v>67.08381189388399</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>39.40281606642064</v>
+        <v>14.46667127807536</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7204647066002831</v>
+        <v>2.843235954600524</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>6.671907716524382</v>
+        <v>0.1516390527204662</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7715</v>
+        <v>8016</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>605.9414629659872</v>
+        <v>623.8958654419929</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>37</v>
+        <v>302</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>64.41214372701467</v>
+        <v>45.00580870824002</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42.37708408711084</v>
+        <v>31.69694170850491</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7695147769670331</v>
+        <v>0.4997884454218033</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.0156479429499769</v>
+        <v>-3.965880053293585</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8039</v>
+        <v>7795</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>590.8735963739393</v>
+        <v>616.6167078386101</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>181.5</v>
+        <v>592</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>67.31379569052297</v>
+        <v>63.68547627600327</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.67915729749135</v>
+        <v>30.61065643788005</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.959123211748154</v>
+        <v>0.6018967524929859</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>4.052030446238996</v>
+        <v>-0.4190140980310133</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6870</v>
+        <v>6907</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>587.6110417091197</v>
+        <v>616.2046470660028</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>304.5</v>
+        <v>232.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.65712025340846</v>
+        <v>75.60165797176452</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19.84370161566733</v>
+        <v>39.40281606642064</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4243578982709417</v>
+        <v>0.7204647066002831</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0159562586510446</v>
+        <v>6.671907716524382</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7788</v>
+        <v>7715</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>582.543440977277</v>
+        <v>605.9414629659872</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>269.5</v>
+        <v>37</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.86034614869735</v>
+        <v>64.41214372701467</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.76737532422656</v>
+        <v>42.37708408711084</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.141312491270753</v>
+        <v>0.7695147769670331</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.052175704533536</v>
+        <v>-0.0156479429499769</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6944</v>
+        <v>8039</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>574.203711704738</v>
+        <v>590.8735963739393</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1035</v>
+        <v>181.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.87420564939911</v>
+        <v>67.31379569052297</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.30900396195756</v>
+        <v>22.67915729749135</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.9337254934794804</v>
+        <v>3.959123211748154</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4634777849020572</v>
+        <v>4.052030446238996</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8046</v>
+        <v>6870</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>573.3115912723812</v>
+        <v>587.6110417091197</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1415</v>
+        <v>304.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>73.13372894521481</v>
+        <v>58.65712025340846</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.49051083999841</v>
+        <v>19.84370161566733</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9311591272381188</v>
+        <v>0.4243578982709417</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>25.83624538801649</v>
+        <v>0.0159562586510446</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8028</v>
+        <v>7788</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>569.9702102254234</v>
+        <v>582.543440977277</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>318.5</v>
+        <v>269.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>53.81242159170633</v>
+        <v>59.86034614869735</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.60402266258358</v>
+        <v>25.76737532422656</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.042528683555464</v>
+        <v>1.141312491270753</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-2.099200092379418</v>
+        <v>-1.052175704533536</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6887</v>
+        <v>6944</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>569.2862514822696</v>
+        <v>574.203711704738</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>39.7</v>
+        <v>1035</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>62.70120795904453</v>
+        <v>56.87420564939911</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>9.492017733428368</v>
+        <v>12.30900396195756</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.828625148226956</v>
+        <v>0.9337254934794804</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3905544666753026</v>
+        <v>0.4634777849020572</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6914</v>
+        <v>8046</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>551.3749044583359</v>
+        <v>573.3115912723812</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>145.5</v>
+        <v>1415</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.07675437471974</v>
+        <v>73.13372894521481</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10.80046152594034</v>
+        <v>22.49051083999841</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.9635072756972088</v>
+        <v>0.9311591272381188</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1928194507456378</v>
+        <v>25.83624538801649</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7799</v>
+        <v>8028</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>546.3627478190244</v>
+        <v>569.9702102254234</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>418.5</v>
+        <v>318.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.20145696660823</v>
+        <v>53.81242159170633</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>33.9477700621575</v>
+        <v>23.60402266258358</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5372224340398756</v>
+        <v>1.042528683555464</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.387406520067092</v>
+        <v>-2.099200092379418</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6863</v>
+        <v>6887</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>544.2968939077989</v>
+        <v>569.2862514822696</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>104</v>
+        <v>39.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>63.17647768102787</v>
+        <v>62.70120795904453</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>24.30086525438426</v>
+        <v>9.492017733428368</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.651293507380073</v>
+        <v>2.828625148226956</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.872115007264077</v>
+        <v>0.3905544666753026</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8042</v>
+        <v>6914</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>541.8173658954142</v>
+        <v>551.3749044583359</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>151.5</v>
+        <v>145.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>43.75955323168514</v>
+        <v>60.07675437471974</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.50957452726955</v>
+        <v>10.80046152594034</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7492706371426775</v>
+        <v>0.9635072756972088</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-7.333157195843526</v>
+        <v>0.1928194507456378</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8043</v>
+        <v>7799</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>539.8634404787075</v>
+        <v>546.3627478190244</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>154.5</v>
+        <v>418.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>40.37915359285505</v>
+        <v>55.20145696660823</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>24.00841998600249</v>
+        <v>33.9477700621575</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4223197384201719</v>
+        <v>0.5372224340398756</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-8.017138477841289</v>
+        <v>-1.387406520067092</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7828</v>
+        <v>6863</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>530.372997854626</v>
+        <v>544.2968939077989</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2015</v>
+        <v>104</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.7928688783942</v>
+        <v>63.17647768102787</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.12187126190044</v>
+        <v>24.30086525438426</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5954955185313244</v>
+        <v>1.651293507380073</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-37.7705942185483</v>
+        <v>1.872115007264077</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6997</v>
+        <v>8042</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>527.5999555160457</v>
+        <v>541.8173658954142</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>76.7</v>
+        <v>151.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.25686446872105</v>
+        <v>43.75955323168514</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8.876532616866783</v>
+        <v>22.50957452726955</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6711166083766954</v>
+        <v>0.7492706371426775</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2368143892420573</v>
+        <v>-7.333157195843526</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7722</v>
+        <v>8043</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>524.0334702282612</v>
+        <v>539.8634404787075</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>306.5</v>
+        <v>154.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>47.74909662873118</v>
+        <v>40.37915359285505</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>32.4545738615536</v>
+        <v>24.00841998600249</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.1936666015791481</v>
+        <v>0.4223197384201719</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-3.028245157688101</v>
+        <v>-8.017138477841289</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7768</v>
+        <v>7828</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>504.8527225828086</v>
+        <v>530.372997854626</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>333</v>
+        <v>2015</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>39.94113382427201</v>
+        <v>52.7928688783942</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20.02466991360205</v>
+        <v>26.12187126190044</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4259128632748729</v>
+        <v>0.5954955185313244</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.5036533166963455</v>
+        <v>-37.7705942185483</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6928</v>
+        <v>6997</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>487.5491989890394</v>
+        <v>527.5999555160457</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>53.5</v>
+        <v>76.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.69840747718746</v>
+        <v>54.25686446872105</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.51858503214486</v>
+        <v>8.876532616866783</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.066825604897008</v>
+        <v>0.6711166083766954</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0929074513424801</v>
+        <v>0.2368143892420573</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7711</v>
+        <v>7722</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>483.1942234251877</v>
+        <v>524.0334702282612</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>317.5</v>
+        <v>306.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>40.22395172950852</v>
+        <v>47.74909662873118</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.49895776484336</v>
+        <v>32.4545738615536</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4686954921749444</v>
+        <v>0.1936666015791481</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.244941570638117</v>
+        <v>-3.028245157688101</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7751</v>
+        <v>7768</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>480.5336687375596</v>
+        <v>504.8527225828086</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1210</v>
+        <v>333</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>38.17006460318032</v>
+        <v>39.94113382427201</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>12.42458885439752</v>
+        <v>20.02466991360205</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.169875830264151</v>
+        <v>0.4259128632748729</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-12.21436890852524</v>
+        <v>-0.5036533166963455</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7734</v>
+        <v>6928</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>478.8340907637507</v>
+        <v>487.5491989890394</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3045</v>
+        <v>53.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.02618886044414</v>
+        <v>55.69840747718746</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.67254328058282</v>
+        <v>32.51858503214486</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.50518953838707</v>
+        <v>1.066825604897008</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-17.41547579436771</v>
+        <v>0.0929074513424801</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6919</v>
+        <v>7711</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>477.3380814163402</v>
+        <v>483.1942234251877</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>109.5</v>
+        <v>317.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.59973097420339</v>
+        <v>40.22395172950852</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.95191256948469</v>
+        <v>23.49895776484336</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.013005207065999</v>
+        <v>0.4686954921749444</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.8997804801936691</v>
+        <v>0.244941570638117</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6994</v>
+        <v>7751</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>455.547644078241</v>
+        <v>480.5336687375596</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>41.3</v>
+        <v>1210</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>31.88537571321157</v>
+        <v>38.17006460318032</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>30.26148371390628</v>
+        <v>12.42458885439752</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2029115618303739</v>
+        <v>1.169875830264151</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1547942470846006</v>
+        <v>-12.21436890852524</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8047</v>
+        <v>7734</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>452.4780421209592</v>
+        <v>478.8340907637507</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>42.75</v>
+        <v>3045</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>38.32753077445907</v>
+        <v>49.02618886044414</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>9.446142976222612</v>
+        <v>16.67254328058282</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.780682611818194</v>
+        <v>2.50518953838707</v>
       </c>
       <c r="K35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.637632834013262</v>
+        <v>-17.41547579436771</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7712</v>
+        <v>6919</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>450.2943157048431</v>
+        <v>477.3380814163402</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>165</v>
+        <v>109.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>42.27276359697029</v>
+        <v>58.59973097420339</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.48430969865101</v>
+        <v>17.95191256948469</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3044575326218889</v>
+        <v>1.013005207065999</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-5.495898327033233</v>
+        <v>0.8997804801936691</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6903</v>
+        <v>6994</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>447.7092578285679</v>
+        <v>455.547644078241</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>406</v>
+        <v>41.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.79882621037282</v>
+        <v>31.88537571321157</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9.72489295995498</v>
+        <v>30.26148371390628</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.171036314173905</v>
+        <v>0.2029115618303739</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.056044016566209</v>
+        <v>-0.1547942470846006</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7703</v>
+        <v>8047</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>438.6842046489618</v>
+        <v>452.4780421209592</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>199.5</v>
+        <v>42.75</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>48.04112518053365</v>
+        <v>38.32753077445907</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11.25781224904358</v>
+        <v>9.446142976222612</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9668633064864984</v>
+        <v>1.780682611818194</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>1</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1014916053628045</v>
+        <v>-0.637632834013262</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7631</v>
+        <v>7712</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>431.6849974926058</v>
+        <v>450.2943157048431</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>145.5</v>
+        <v>165</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.43060928094444</v>
+        <v>42.27276359697029</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15.24959327982282</v>
+        <v>30.48430969865101</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2579164522211376</v>
+        <v>0.3044575326218889</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-2.274470946629081</v>
+        <v>-5.495898327033233</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6934</v>
+        <v>6903</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>431.5890682356439</v>
+        <v>447.7092578285679</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>81.5</v>
+        <v>406</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>68.69835102321449</v>
+        <v>54.79882621037282</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.58660910634444</v>
+        <v>9.72489295995498</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.013702945345724</v>
+        <v>2.171036314173905</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.918873476772212</v>
+        <v>1.056044016566209</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7818</v>
+        <v>7703</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>429.005894658725</v>
+        <v>438.6842046489618</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>70</v>
+        <v>199.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>56.27211445688394</v>
+        <v>48.04112518053365</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.78609349364739</v>
+        <v>11.25781224904358</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6480783857705852</v>
+        <v>0.9668633064864984</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.260501129463116</v>
+        <v>0.1014916053628045</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6916</v>
+        <v>7631</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>425.0963237406601</v>
+        <v>431.6849974926058</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>20.75</v>
+        <v>145.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.97301834035539</v>
+        <v>50.43060928094444</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.1695074922512</v>
+        <v>15.24959327982282</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3385869456887821</v>
+        <v>0.2579164522211376</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1421609503295837</v>
+        <v>-2.274470946629081</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7717</v>
+        <v>6934</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>417.7617200886722</v>
+        <v>431.5890682356439</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>532</v>
+        <v>81.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.89261909785152</v>
+        <v>68.69835102321449</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.95828526445645</v>
+        <v>23.58660910634444</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.286439678831756</v>
+        <v>1.013702945345724</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>13.92111555009883</v>
+        <v>1.918873476772212</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6951</v>
+        <v>7818</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>410.3454797506713</v>
+        <v>429.005894658725</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>33.46615159999655</v>
+        <v>56.27211445688394</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>28.01422456594859</v>
+        <v>27.78609349364739</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.117224150425264</v>
+        <v>0.6480783857705852</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.5241333048332082</v>
+        <v>1.260501129463116</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7839</v>
+        <v>6916</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>409.6613230407622</v>
+        <v>425.0963237406601</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>44.5</v>
+        <v>20.75</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45.19793427379516</v>
+        <v>53.97301834035539</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>11.10050983329286</v>
+        <v>16.1695074922512</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3869041523585861</v>
+        <v>0.3385869456887821</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2352590017388247</v>
+        <v>-0.1421609503295837</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7547</v>
+        <v>7717</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>405.8090347793605</v>
+        <v>417.7617200886722</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>54.8</v>
+        <v>532</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>35.68634397858176</v>
+        <v>53.89261909785152</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11.84686663946293</v>
+        <v>21.95828526445645</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.580255105802551</v>
+        <v>1.286439678831756</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.013004513946323</v>
+        <v>13.92111555009883</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6861</v>
+        <v>6951</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>399.1147866109599</v>
+        <v>410.3454797506713</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>238.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>29.85308458666371</v>
+        <v>33.46615159999655</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.57764590407324</v>
+        <v>28.01422456594859</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.19248342189477</v>
+        <v>1.117224150425264</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-9.3305678273632</v>
+        <v>-0.5241333048332082</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7732</v>
+        <v>7839</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>396.1295038398767</v>
+        <v>409.6613230407622</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>35.75</v>
+        <v>44.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.80271833578723</v>
+        <v>45.19793427379516</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9.381527340604032</v>
+        <v>11.10050983329286</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.61764335948309</v>
+        <v>0.3869041523585861</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.967432906972697</v>
+        <v>0.2352590017388247</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7786</v>
+        <v>7547</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>391.7752207043911</v>
+        <v>405.8090347793605</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>131</v>
+        <v>54.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.30071726193145</v>
+        <v>35.68634397858176</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.48340607984492</v>
+        <v>11.84686663946293</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5567938278698275</v>
+        <v>0.580255105802551</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.8909408753875582</v>
+        <v>0.013004513946323</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7827</v>
+        <v>6861</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>382.2030802938407</v>
+        <v>399.1147866109599</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>165</v>
+        <v>238.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.91998742016457</v>
+        <v>29.85308458666371</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.91809295550532</v>
+        <v>18.57764590407324</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3620185454374224</v>
+        <v>1.19248342189477</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.8730492950164157</v>
+        <v>-9.3305678273632</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7753</v>
+        <v>7732</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>376.0435013413777</v>
+        <v>396.1295038398767</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>41.4</v>
+        <v>35.75</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>43.75823833660292</v>
+        <v>51.80271833578723</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.91878394506676</v>
+        <v>9.381527340604032</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5438206445036563</v>
+        <v>1.61764335948309</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1548470598278105</v>
+        <v>0.967432906972697</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7402</v>
+        <v>7786</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>369.494058559344</v>
+        <v>391.7752207043911</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>135.5</v>
+        <v>131</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>62.092893179249</v>
+        <v>57.30071726193145</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>34.27729910464573</v>
+        <v>17.48340607984492</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8494058559343937</v>
+        <v>0.5567938278698275</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.457050402630138</v>
+        <v>0.8909408753875582</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6923</v>
+        <v>7827</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>363.5853523633136</v>
+        <v>382.2030802938407</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>80.2</v>
+        <v>165</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>56.41911447979479</v>
+        <v>50.91998742016457</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12.72847836003552</v>
+        <v>19.91809295550532</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.013140362364428</v>
+        <v>0.3620185454374224</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.4732921566625062</v>
+        <v>-0.8730492950164157</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8040</v>
+        <v>7753</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>358.5257240662757</v>
+        <v>376.0435013413777</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>41.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>38.35015484242662</v>
+        <v>43.75823833660292</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.77733855563348</v>
+        <v>24.91878394506676</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1759839121398052</v>
+        <v>0.5438206445036563</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-2.708682464992914</v>
+        <v>-0.1548470598278105</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6885</v>
+        <v>7402</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>357.8070819691056</v>
+        <v>369.494058559344</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>21.6</v>
+        <v>135.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.6154830393362</v>
+        <v>62.092893179249</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.12150637013461</v>
+        <v>34.27729910464573</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6822309219328904</v>
+        <v>0.8494058559343937</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0301250931255899</v>
+        <v>2.457050402630138</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6983</v>
+        <v>6923</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>353.8015700740324</v>
+        <v>363.5853523633136</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>358</v>
+        <v>80.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.52306393306414</v>
+        <v>56.41911447979479</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>10.19468028083352</v>
+        <v>12.72847836003552</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8926918180766115</v>
+        <v>1.013140362364428</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1.028547770150049</v>
+        <v>0.4732921566625062</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7810</v>
+        <v>8040</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>350.2764268902565</v>
+        <v>358.5257240662757</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>201.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.03388760138093</v>
+        <v>38.35015484242662</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.45282986526622</v>
+        <v>24.77733855563348</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.21266798673681</v>
+        <v>0.1759839121398052</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.8354739316338886</v>
+        <v>-2.708682464992914</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6902</v>
+        <v>6885</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>348.1830929072075</v>
+        <v>357.8070819691056</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>133</v>
+        <v>21.6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.51215708200614</v>
+        <v>46.6154830393362</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17.06193564902154</v>
+        <v>16.12150637013461</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.1707842424728874</v>
+        <v>0.6822309219328904</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.6563539292990908</v>
+        <v>0.0301250931255899</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7769</v>
+        <v>6983</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>347.6639034566356</v>
+        <v>353.8015700740324</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>6720</v>
+        <v>358</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>49.93451350020698</v>
+        <v>48.52306393306414</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12.65398627122789</v>
+        <v>10.19468028083352</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8112544831957997</v>
+        <v>0.8926918180766115</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-24.25651864037179</v>
+        <v>1.028547770150049</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7744</v>
+        <v>7810</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>341.6528957093272</v>
+        <v>350.2764268902565</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>459.5</v>
+        <v>201.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.46909381628495</v>
+        <v>43.03388760138093</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.12578848054706</v>
+        <v>15.45282986526622</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2235650683762053</v>
+        <v>1.21266798673681</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.614446217107194</v>
+        <v>0.8354739316338886</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8032</v>
+        <v>6902</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>329.2628013221743</v>
+        <v>348.1830929072075</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>33.52930934865437</v>
+        <v>50.51215708200614</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.90000717290756</v>
+        <v>17.06193564902154</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3475771658977558</v>
+        <v>0.1707842424728874</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.675231885097592</v>
+        <v>-0.6563539292990908</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6899</v>
+        <v>7769</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>327.3839349191676</v>
+        <v>347.6639034566356</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>52.6</v>
+        <v>6720</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>29.11997068396471</v>
+        <v>49.93451350020698</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.45647280780199</v>
+        <v>12.65398627122789</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.504824153343955</v>
+        <v>0.8112544831957997</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.6477459487358992</v>
+        <v>-24.25651864037179</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8044</v>
+        <v>7744</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>318.7804002462844</v>
+        <v>341.6528957093272</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>27.65</v>
+        <v>459.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.42211316714298</v>
+        <v>46.46909381628495</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13.86063390565164</v>
+        <v>11.12578848054706</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3561477108506837</v>
+        <v>0.2235650683762053</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.2494858539586324</v>
+        <v>1.614446217107194</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7760</v>
+        <v>8032</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>318.5403483384999</v>
+        <v>329.2628013221743</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>34.5</v>
+        <v>39</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.6590615137519</v>
+        <v>33.52930934865437</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>30.53336703159112</v>
+        <v>21.90000717290756</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.302081782691552</v>
+        <v>0.3475771658977558</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.055338520092542</v>
+        <v>-0.675231885097592</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7791</v>
+        <v>6899</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>314.7563594510881</v>
+        <v>327.3839349191676</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>63.4</v>
+        <v>52.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.76002232169298</v>
+        <v>29.11997068396471</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.54278352776072</v>
+        <v>18.45647280780199</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6477220220752952</v>
+        <v>1.504824153343955</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2119061825589784</v>
+        <v>-0.6477459487358992</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6996</v>
+        <v>8044</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>313.9690245830028</v>
+        <v>318.7804002462844</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>181.5</v>
+        <v>27.65</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>39.62724225746963</v>
+        <v>47.42211316714298</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20.48511528933517</v>
+        <v>13.86063390565164</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7681228797493821</v>
+        <v>0.3561477108506837</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-2.294358817787552</v>
+        <v>-0.2494858539586324</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6873</v>
+        <v>7760</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>309.3940147503193</v>
+        <v>318.5403483384999</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>87.3</v>
+        <v>34.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.96003033704732</v>
+        <v>52.6590615137519</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.69380953093706</v>
+        <v>30.53336703159112</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6370013942531131</v>
+        <v>0.302081782691552</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.7105365840814321</v>
+        <v>0.055338520092542</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7728</v>
+        <v>7791</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>305.621949141353</v>
+        <v>314.7563594510881</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>674</v>
+        <v>63.4</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.40497721117102</v>
+        <v>52.76002232169298</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11.13134247348305</v>
+        <v>12.54278352776072</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4903961242519236</v>
+        <v>0.6477220220752952</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>2.28319993204672</v>
+        <v>0.2119061825589784</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7820</v>
+        <v>6996</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>303.6576240863975</v>
+        <v>313.9690245830028</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>116</v>
+        <v>181.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.97863028883042</v>
+        <v>39.62724225746963</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.30903192317608</v>
+        <v>20.48511528933517</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6651385942683049</v>
+        <v>0.7681228797493821</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>1.011187543268358</v>
+        <v>-2.294358817787552</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6869</v>
+        <v>6873</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>301.0776449131102</v>
+        <v>309.3940147503193</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>69.8</v>
+        <v>87.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.01802323208031</v>
+        <v>52.96003033704732</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>23.78812843303185</v>
+        <v>16.69380953093706</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7738262155683596</v>
+        <v>0.6370013942531131</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0574036513574398</v>
+        <v>0.7105365840814321</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6952</v>
+        <v>7728</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>292.8872863679388</v>
+        <v>305.621949141353</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>35.6</v>
+        <v>674</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.72403898142804</v>
+        <v>47.40497721117102</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.10690509930933</v>
+        <v>11.13134247348305</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.376553531785079</v>
+        <v>0.4903961242519236</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0182204825880845</v>
+        <v>2.28319993204672</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7747</v>
+        <v>7820</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>292.8691023077339</v>
+        <v>303.6576240863975</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>39.04581610338567</v>
+        <v>42.97863028883042</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9.014886112697528</v>
+        <v>19.30903192317608</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.1869102307733881</v>
+        <v>0.6651385942683049</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-2.067672189513109</v>
+        <v>1.011187543268358</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7704</v>
+        <v>6869</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>292.258131323221</v>
+        <v>301.0776449131102</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>56.8</v>
+        <v>69.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>37.00625075367026</v>
+        <v>38.01802323208031</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.02984923410444</v>
+        <v>23.78812843303185</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3756651024235301</v>
+        <v>0.7738262155683596</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.7355605898065241</v>
+        <v>0.0574036513574398</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6913</v>
+        <v>6952</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>287.9531069206056</v>
+        <v>292.8872863679388</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>125.5</v>
+        <v>35.6</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.85798493775784</v>
+        <v>46.72403898142804</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.24801044548135</v>
+        <v>15.10690509930933</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.602164738425309</v>
+        <v>1.376553531785079</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.9046696587189657</v>
+        <v>0.0182204825880845</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6953</v>
+        <v>7747</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>287.8192415136048</v>
+        <v>292.8691023077339</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>231.5</v>
+        <v>114</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>48.03348092166809</v>
+        <v>39.04581610338567</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11.05356357206889</v>
+        <v>9.014886112697528</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8669809763167067</v>
+        <v>0.1869102307733881</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0354739736886959</v>
+        <v>-2.067672189513109</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8045</v>
+        <v>7704</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>285.6248098348408</v>
+        <v>292.258131323221</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>57.5</v>
+        <v>56.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>39.494431303734</v>
+        <v>37.00625075367026</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>12.55268766871708</v>
+        <v>14.02984923410444</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7308389397956923</v>
+        <v>0.3756651024235301</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0496095940608793</v>
+        <v>-0.7355605898065241</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6955</v>
+        <v>6913</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>285.470455531343</v>
+        <v>287.9531069206056</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>115</v>
+        <v>125.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.95614936847616</v>
+        <v>49.85798493775784</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6.336224278527201</v>
+        <v>15.24801044548135</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8158977110157367</v>
+        <v>0.602164738425309</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.9512000330478418</v>
+        <v>0.9046696587189657</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6965</v>
+        <v>6953</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>281.9872793334087</v>
+        <v>287.8192415136048</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>79.7</v>
+        <v>231.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.86429538294137</v>
+        <v>48.03348092166809</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>24.16425560204148</v>
+        <v>11.05356357206889</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.7827427625553919</v>
+        <v>0.8669809763167067</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1780638732424208</v>
+        <v>-0.0354739736886959</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7823</v>
+        <v>8045</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>269.3461182022802</v>
+        <v>285.6248098348408</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>84.8</v>
+        <v>57.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.46849646126253</v>
+        <v>39.494431303734</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>27.75538045465761</v>
+        <v>12.55268766871708</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5072258851895399</v>
+        <v>0.7308389397956923</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>1.130957406812025</v>
+        <v>0.0496095940608793</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7705</v>
+        <v>6955</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>268.2228706318549</v>
+        <v>285.470455531343</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>31.05</v>
+        <v>115</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.98125491399973</v>
+        <v>47.95614936847616</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.50235440827733</v>
+        <v>6.336224278527201</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6915697988733741</v>
+        <v>0.8158977110157367</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.1232855832577055</v>
+        <v>0.9512000330478418</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7750</v>
+        <v>6965</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>267.4441548049223</v>
+        <v>281.9872793334087</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1990</v>
+        <v>79.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>40.3298071217609</v>
+        <v>50.86429538294137</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>15.49752403941535</v>
+        <v>24.16425560204148</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5670146351448163</v>
+        <v>0.7827427625553919</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-6.152071522609155</v>
+        <v>0.1780638732424208</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6877</v>
+        <v>7823</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>266.4341091530268</v>
+        <v>269.3461182022802</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>136</v>
+        <v>84.8</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>50.25574661498111</v>
+        <v>50.46849646126253</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.17713011377562</v>
+        <v>27.75538045465761</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2476105964840981</v>
+        <v>0.5072258851895399</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.4340491009871</v>
+        <v>1.130957406812025</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6895</v>
+        <v>7705</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>265.0916048318693</v>
+        <v>268.2228706318549</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>128.5</v>
+        <v>31.05</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>29.66555113491764</v>
+        <v>45.98125491399973</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.58405734603447</v>
+        <v>19.50235440827733</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7867310852795609</v>
+        <v>0.6915697988733741</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-2.101341818630686</v>
+        <v>-0.1232855832577055</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7822</v>
+        <v>7750</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>260.3597601843186</v>
+        <v>267.4441548049223</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>979</v>
+        <v>1990</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.21471872012194</v>
+        <v>40.3298071217609</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.64647177313584</v>
+        <v>15.49752403941535</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5663843462365643</v>
+        <v>0.5670146351448163</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-17.7861556572532</v>
+        <v>-6.152071522609155</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7805</v>
+        <v>6877</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>249.4007107794154</v>
+        <v>266.4341091530268</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>628</v>
+        <v>136</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>32.42519014443339</v>
+        <v>50.25574661498111</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>33.06399569698215</v>
+        <v>13.17713011377562</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3435331589125242</v>
+        <v>0.2476105964840981</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-2.510324650790881</v>
+        <v>1.4340491009871</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6937</v>
+        <v>6895</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>247.4027048410454</v>
+        <v>265.0916048318693</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>262.5</v>
+        <v>128.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.99902315993741</v>
+        <v>29.66555113491764</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.17222286014739</v>
+        <v>23.58405734603447</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5986438098155935</v>
+        <v>0.7867310852795609</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.6522389529827368</v>
+        <v>-2.101341818630686</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7770</v>
+        <v>7822</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>242.1135670391184</v>
+        <v>260.3597601843186</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>41.95</v>
+        <v>979</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.83242890510052</v>
+        <v>41.21471872012194</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5.824369038278944</v>
+        <v>17.64647177313584</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3483578003458988</v>
+        <v>0.5663843462365643</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0535712679492249</v>
+        <v>-17.7861556572532</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7792</v>
+        <v>7805</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>237.4438608697276</v>
+        <v>249.4007107794154</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>234.5</v>
+        <v>628</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>36.13325899560962</v>
+        <v>32.42519014443339</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>21.21410951390336</v>
+        <v>33.06399569698215</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2660674384027666</v>
+        <v>0.3435331589125242</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.198713441997192</v>
+        <v>-2.510324650790881</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7821</v>
+        <v>6937</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>236.6264928429999</v>
+        <v>247.4027048410454</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40.8</v>
+        <v>262.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>35.03841284109185</v>
+        <v>44.99902315993741</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>30.15749265590802</v>
+        <v>13.17222286014739</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8304192890842991</v>
+        <v>0.5986438098155935</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0060453836480178</v>
+        <v>-0.6522389529827368</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7842</v>
+        <v>7770</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>233.6803216316297</v>
+        <v>242.1135670391184</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>41.95</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.44947285118645</v>
+        <v>46.83242890510052</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.27604967431095</v>
+        <v>5.824369038278944</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4519658538911711</v>
+        <v>0.3483578003458988</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.8171397328843213</v>
+        <v>0.0535712679492249</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6931</v>
+        <v>7792</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>232.1403769003345</v>
+        <v>237.4438608697276</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>39.55</v>
+        <v>234.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>40.51572511073001</v>
+        <v>36.13325899560962</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.89730141038907</v>
+        <v>21.21410951390336</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.106434540886331</v>
+        <v>0.2660674384027666</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0254929522599588</v>
+        <v>-1.198713441997192</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7738</v>
+        <v>7821</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>228.7348941074872</v>
+        <v>236.6264928429999</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>167</v>
+        <v>40.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.76500468003979</v>
+        <v>35.03841284109185</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>25.0276089629678</v>
+        <v>30.15749265590802</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.194938166342377</v>
+        <v>0.8304192890842991</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0761142886851212</v>
+        <v>-0.0060453836480178</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6862</v>
+        <v>7842</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>226.765936859688</v>
+        <v>233.6803216316297</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>170</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.52664563630736</v>
+        <v>41.44947285118645</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.63265529319695</v>
+        <v>17.27604967431095</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2185581776468581</v>
+        <v>0.4519658538911711</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-3.659684968632956</v>
+        <v>0.8171397328843213</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6910</v>
+        <v>6931</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>223.9310320504773</v>
+        <v>232.1403769003345</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>26</v>
+        <v>39.55</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>30.59268656244625</v>
+        <v>40.51572511073001</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.9059605756823</v>
+        <v>14.89730141038907</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.093446358366489</v>
+        <v>1.106434540886331</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1296936485128925</v>
+        <v>0.0254929522599588</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7772</v>
+        <v>7738</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>219.0435116938987</v>
+        <v>228.7348941074872</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>104.5</v>
+        <v>167</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>30.1490301497994</v>
+        <v>44.76500468003979</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.55353620911582</v>
+        <v>25.0276089629678</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6162513266419875</v>
+        <v>0.194938166342377</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.942442329266555</v>
+        <v>-0.0761142886851212</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7740</v>
+        <v>6862</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>218.4557702975701</v>
+        <v>226.765936859688</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>54.98922935767956</v>
+        <v>40.52664563630736</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.96664284621528</v>
+        <v>16.63265529319695</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.409399600163961</v>
+        <v>0.2185581776468581</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>1.622124963504262</v>
+        <v>-3.659684968632956</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6906</v>
+        <v>6910</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>218.2193863583717</v>
+        <v>223.9310320504773</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>26</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>30.02604541594624</v>
+        <v>30.59268656244625</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.5309460689857</v>
+        <v>18.9059605756823</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5906374345419565</v>
+        <v>1.093446358366489</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-2.053689563816406</v>
+        <v>-0.1296936485128925</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7556</v>
+        <v>7772</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>214.497475335897</v>
+        <v>219.0435116938987</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>235</v>
+        <v>104.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>30.34583965614206</v>
+        <v>30.1490301497994</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.3110633756383</v>
+        <v>12.55353620911582</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4600523850590374</v>
+        <v>0.6162513266419875</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-5.837877814430686</v>
+        <v>-1.942442329266555</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7721</v>
+        <v>7740</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>209.0303170152557</v>
+        <v>218.4557702975701</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.15716234115769</v>
+        <v>54.98922935767956</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>10.34029566641989</v>
+        <v>16.96664284621528</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5268649073231669</v>
+        <v>1.409399600163961</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.4414100471204314</v>
+        <v>1.622124963504262</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7780</v>
+        <v>6906</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>208.834891596147</v>
+        <v>218.2193863583717</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>17.85</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.83370693885674</v>
+        <v>30.02604541594624</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.49568840156486</v>
+        <v>19.5309460689857</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.42741982450969</v>
+        <v>0.5906374345419565</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0299372437662993</v>
+        <v>-2.053689563816406</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6854</v>
+        <v>7556</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>207.1135454645433</v>
+        <v>214.497475335897</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>105.5</v>
+        <v>235</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>24.27748957914653</v>
+        <v>30.34583965614206</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>28.10382948579656</v>
+        <v>17.3110633756383</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.289658608454331</v>
+        <v>0.4600523850590374</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.009425222823588</v>
+        <v>-5.837877814430686</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6909</v>
+        <v>7721</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>202.0374388326813</v>
+        <v>209.0303170152557</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>47.95</v>
+        <v>68</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.09777112106898</v>
+        <v>40.15716234115769</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.87501409023207</v>
+        <v>10.34029566641989</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2516861863671637</v>
+        <v>0.5268649073231669</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.128975809633469</v>
+        <v>-0.4414100471204314</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6890</v>
+        <v>7780</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>201.5091736842248</v>
+        <v>208.834891596147</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>176</v>
+        <v>17.85</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>37.55919325979511</v>
+        <v>42.83370693885674</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.04792738552979</v>
+        <v>16.49568840156486</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7037704870242951</v>
+        <v>0.42741982450969</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-6.184499160397161</v>
+        <v>-0.0299372437662993</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6933</v>
+        <v>6854</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>201.2696465311909</v>
+        <v>207.1135454645433</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>170.5</v>
+        <v>105.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>59.10826990187172</v>
+        <v>24.27748957914653</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.7918410962153</v>
+        <v>28.10382948579656</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.50094664542689</v>
+        <v>1.289658608454331</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>3.300888611236188</v>
+        <v>-1.009425222823588</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6865</v>
+        <v>6909</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>201.1111820009928</v>
+        <v>202.0374388326813</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>25.8</v>
+        <v>47.95</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>49.98831485228835</v>
+        <v>40.09777112106898</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.00466040584587</v>
+        <v>16.87501409023207</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3.597272479316302</v>
+        <v>0.2516861863671637</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,28 +6029,28 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1483092865499073</v>
+        <v>-1.128975809633469</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6922</v>
+        <v>6890</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>201.0923540636462</v>
+        <v>201.5091736842248</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>176</v>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.86036441654017</v>
+        <v>37.55919325979511</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.59213627889309</v>
+        <v>18.04792738552979</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4969904594951236</v>
+        <v>0.7037704870242951</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0314559120216524</v>
+        <v>-6.184499160397161</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6924</v>
+        <v>6933</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>200.1207801063585</v>
+        <v>201.2696465311909</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>118.5</v>
+        <v>170.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.07729932627498</v>
+        <v>59.10826990187172</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.40658720106777</v>
+        <v>16.7918410962153</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7325698078647327</v>
+        <v>2.50094664542689</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0438580028641384</v>
+        <v>3.300888611236188</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, rsi_strong, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8034</v>
+        <v>6865</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>197.9335085463498</v>
+        <v>201.1111820009928</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>20.1</v>
+        <v>25.8</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>22.42259859938483</v>
+        <v>49.98831485228835</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>27.8317905162092</v>
+        <v>14.00466040584587</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4165053602727262</v>
+        <v>3.597272479316302</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>1</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1884277884310795</v>
+        <v>-0.1483092865499073</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6971</v>
+        <v>6922</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>195.1937156080662</v>
+        <v>201.0923540636462</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>27.1</v>
+        <v>176</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.20561451243238</v>
+        <v>44.86036441654017</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.74903296448181</v>
+        <v>14.59213627889309</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>3.527133317670951</v>
+        <v>0.4969904594951236</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.06943791571465489</v>
+        <v>-0.0314559120216524</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6894</v>
+        <v>6924</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>194.1126108359882</v>
+        <v>200.1207801063585</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>350</v>
+        <v>118.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45.55330827514897</v>
+        <v>44.07729932627498</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.92105093839085</v>
+        <v>14.40658720106777</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.706721701169966</v>
+        <v>0.7325698078647327</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-2.095349714996478</v>
+        <v>-0.0438580028641384</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7749</v>
+        <v>8034</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>189.6183989357754</v>
+        <v>197.9335085463498</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>401</v>
+        <v>20.1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>35.53020697161907</v>
+        <v>22.42259859938483</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.52939237753781</v>
+        <v>27.8317905162092</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4726298949073504</v>
+        <v>0.4165053602727262</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-3.72292349726321</v>
+        <v>-0.1884277884310795</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6969</v>
+        <v>6971</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>185.9798971078961</v>
+        <v>195.1937156080662</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>25.85</v>
+        <v>27.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>49.61278655129085</v>
+        <v>43.20561451243238</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21.70826486100153</v>
+        <v>17.74903296448181</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5667441710172783</v>
+        <v>3.527133317670951</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.203978105555401</v>
+        <v>-0.06943791571465489</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6962</v>
+        <v>6894</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>184.602681836297</v>
+        <v>194.1126108359882</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>35.05</v>
+        <v>350</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.03318434178549</v>
+        <v>45.55330827514897</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.12795390909206</v>
+        <v>15.92105093839085</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4431935274713784</v>
+        <v>0.706721701169966</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.4997413779771494</v>
+        <v>-2.095349714996478</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6936</v>
+        <v>7749</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>174.6669504932753</v>
+        <v>189.6183989357754</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>32.25</v>
+        <v>401</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.06890256097836</v>
+        <v>35.53020697161907</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.1716233753322</v>
+        <v>17.52939237753781</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.051210454416166</v>
+        <v>0.4726298949073504</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0363310813143483</v>
+        <v>-3.72292349726321</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6855</v>
+        <v>6969</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>171.5570033133146</v>
+        <v>185.9798971078961</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>119</v>
+        <v>25.85</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.57483492382016</v>
+        <v>49.61278655129085</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>9.866071742868078</v>
+        <v>21.70826486100153</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3111898890258939</v>
+        <v>0.5667441710172783</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-2.256145819488148</v>
+        <v>0.203978105555401</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6988</v>
+        <v>6962</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>168.6701375279127</v>
+        <v>184.602681836297</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>13.6</v>
+        <v>35.05</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.70912852666512</v>
+        <v>42.03318434178549</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>11.45319629506916</v>
+        <v>15.12795390909206</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6164103854876448</v>
+        <v>0.4431935274713784</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0571805344974538</v>
+        <v>-0.4997413779771494</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6859</v>
+        <v>6936</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>157.1548124067853</v>
+        <v>174.6669504932753</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>108.5</v>
+        <v>32.25</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>30.8801803686848</v>
+        <v>40.06890256097836</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>19.52184542643096</v>
+        <v>16.1716233753322</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.2358813020760544</v>
+        <v>1.051210454416166</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-2.020780835567427</v>
+        <v>-0.0363310813143483</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6925</v>
+        <v>6855</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>155.4573230400539</v>
+        <v>171.5570033133146</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>56.7</v>
+        <v>119</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>38.31323901562761</v>
+        <v>51.57483492382016</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>10.81703870448598</v>
+        <v>9.866071742868078</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.1920661657574362</v>
+        <v>0.3111898890258939</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.3188262487286777</v>
+        <v>-2.256145819488148</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>8011</v>
+        <v>6988</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>154.2847389098362</v>
+        <v>168.6701375279127</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>17.05</v>
+        <v>13.6</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>41.44408830824862</v>
+        <v>42.70912852666512</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.82629854372374</v>
+        <v>11.45319629506916</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5225520685854094</v>
+        <v>0.6164103854876448</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0351836383778846</v>
+        <v>0.0571805344974538</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>8038</v>
+        <v>6859</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>145.9750543499354</v>
+        <v>157.1548124067853</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>38.55</v>
+        <v>108.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.83626859002016</v>
+        <v>30.8801803686848</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>18.29182427706892</v>
+        <v>19.52184542643096</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3229797710016976</v>
+        <v>0.2358813020760544</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1283408313904032</v>
+        <v>-2.020780835567427</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6918</v>
+        <v>6925</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>140.794884983465</v>
+        <v>155.4573230400539</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>73.5</v>
+        <v>56.7</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>48.61741231219863</v>
+        <v>38.31323901562761</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.91148118422108</v>
+        <v>10.81703870448598</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.600259220634515</v>
+        <v>0.1920661657574362</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0659336386757407</v>
+        <v>-0.3188262487286777</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>7803</v>
+        <v>8011</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>140.115426796919</v>
+        <v>154.2847389098362</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>22.95</v>
+        <v>17.05</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.36878830140389</v>
+        <v>41.44408830824862</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>13.60778878855449</v>
+        <v>16.82629854372374</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5644403684891921</v>
+        <v>0.5225520685854094</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.09975853848100021</v>
+        <v>-0.0351836383778846</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6921</v>
+        <v>8038</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>138.62136141118</v>
+        <v>145.9750543499354</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>67.7</v>
+        <v>38.55</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>41.65723458299898</v>
+        <v>43.83626859002016</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.68880108593578</v>
+        <v>18.29182427706892</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4354408400368305</v>
+        <v>0.3229797710016976</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.1818735173355219</v>
+        <v>-0.1283408313904032</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7730</v>
+        <v>6918</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>124.4067272091883</v>
+        <v>140.794884983465</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>179</v>
+        <v>73.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>45.8948728258826</v>
+        <v>48.61741231219863</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>11.42079680304481</v>
+        <v>15.91148118422108</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.6701749406228236</v>
+        <v>0.600259220634515</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.5185113763172791</v>
+        <v>0.0659336386757407</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7765</v>
+        <v>7803</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>107.2126208766314</v>
+        <v>140.115426796919</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>222.5</v>
+        <v>22.95</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>40.613760810872</v>
+        <v>46.36878830140389</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.68672137275898</v>
+        <v>13.60778878855449</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.3348697463211444</v>
+        <v>0.5644403684891921</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.3647172529447022</v>
+        <v>0.09975853848100021</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>7736</v>
+        <v>6921</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>96.09028518541125</v>
+        <v>138.62136141118</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>70.8</v>
+        <v>67.7</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45.36213064412468</v>
+        <v>41.65723458299898</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>15.39472027329664</v>
+        <v>18.68880108593578</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.338490034132078</v>
+        <v>0.4354408400368305</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,62 +7142,221 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0807465508387581</v>
+        <v>0.1818735173355219</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>7730</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>暉盛-創</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>124.4067272091883</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>45.8948728258826</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>11.42079680304481</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.6701749406228236</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.5185113763172791</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>7765</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>中華資安</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>107.2126208766314</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>40.613760810872</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>18.68672137275898</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.3348697463211444</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.3647172529447022</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>7736</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>虎山</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>96.09028518541125</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>45.36213064412468</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>15.39472027329664</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>1.338490034132078</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>0.0807465508387581</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
         <v>6908</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>宏碁遊戲-創</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
         <v>60.53541061856792</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E130" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
         <v>40.65508619752401</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I130" s="2" t="n">
         <v>18.70197480429296</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J130" s="2" t="n">
         <v>0.9961184584070736</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
         <v>-0.0365103218110013</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O130" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
